--- a/4_outputs/final/Table11.xlsx
+++ b/4_outputs/final/Table11.xlsx
@@ -417,356 +417,572 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr"/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>H1a</t>
+          <t>Config</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>H1b</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>H1c</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>H1d</t>
+          <t>CV macro-F1</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cov. gap</t>
+          <t>MLP 3L/256h, lr=0.0003 (best)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dominance</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Research cov.\</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Policy cov.\</t>
+          <t>0.8192 ± 0.0032</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sliced Wasserstein</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>+0.554^*</t>
+          <t>MLP 2L/256h, lr=0.0003</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+0.061</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>+0.539^*</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>+0.397</t>
+          <t>0.8184 ± 0.0030</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Linear MMD</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>+0.603^*</t>
+          <t>MLP 6L/384h, lr=0.0003</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+0.022</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>+0.466^</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>+0.439^</t>
+          <t>0.8183 ± 0.0023</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Energy distance</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>+0.537^*</t>
+          <t>MLP 2L/384h, lr=0.0003</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+0.074</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>+0.532^*</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>+0.384</t>
+          <t>0.8183 ± 0.0022</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Squared RBF MMD</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+0.473^</t>
+          <t>MLP 4L/256h, lr=0.001</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+0.113</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>+0.551^*</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>+0.296</t>
+          <t>0.8181 ± 0.0017</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Exact EMD</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>+0.304</t>
+          <t>MLP 2L/256h, lr=0.001</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+0.147</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>+0.167</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>+0.217</t>
+          <t>0.8180 ± 0.0038</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Chamfer</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>+0.103</t>
+          <t>MLP 3L/384h, lr=0.0003</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.115</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>-0.350</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>-0.006</t>
+          <t>0.8176 ± 0.0015</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Modified Hausdorff</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>+0.159</t>
+          <t>MLP 4L/384h, lr=0.0003</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+0.152</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>+0.127</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>+0.066</t>
+          <t>0.8175 ± 0.0017</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Gaussian-2-Wasserstein</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-0.007</t>
+          <t>MLP 4L/256h, lr=0.0003</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+0.240</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>+0.262</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>-0.042</t>
+          <t>0.8169 ± 0.0024</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sinkhorn</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-0.199</t>
+          <t>MLP 6L/256h, lr=0.0003</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+0.397</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>-0.176</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>-0.505^*</t>
+          <t>0.8168 ± 0.0026</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C2ST AUC</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>+0.270</t>
+          <t>MLP 3L/256h, lr=0.001</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+0.275</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>+0.375</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>-0.139</t>
+          <t>0.8165 ± 0.0030</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Grassmann</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>-0.186</t>
+          <t>MLP 2L/384h, lr=0.001</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+0.034</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>+0.012</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>-0.228</t>
+          <t>0.8162 ± 0.0053</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>MLP 6L/384h, lr=0.001</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0.8156 ± 0.0039</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>MLP 6L/256h, lr=0.001</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0.8153 ± 0.0027</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>MLP 4L/384h, lr=0.001</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0.8151 ± 0.0024</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>MLP 3L/384h, lr=0.001</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0.8151 ± 0.0015</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>LR C=3.0, cw=None (chosen)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0.8101 ± 0.0020</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>LR C=2.0, cw=None</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0.8098 ± 0.0018</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>LR C=5.0, cw=None</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0.8097 ± 0.0017</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>LR C=1.0, cw=None</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0.8087 ± 0.0025</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>LR C=3.0, cw=balanced</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0.8079 ± 0.0014</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>LR C=2.0, cw=balanced</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0.8077 ± 0.0016</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>LR C=10.0, cw=None</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0.8075 ± 0.0020</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>LR C=5.0, cw=balanced</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0.8073 ± 0.0017</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>LR C=1.0, cw=balanced</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0.8069 ± 0.0026</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>LR C=10.0, cw=balanced</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>0.8063 ± 0.0013</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>LR C=30.0, cw=None</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>0.8039 ± 0.0023</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>LR C=30.0, cw=balanced</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>0.8022 ± 0.0016</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>LR C=100.0, cw=None</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>0.7967 ± 0.0010</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>LR C=100.0, cw=balanced</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>0.7942 ± 0.0017</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>LR C=0.1, cw=balanced</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>0.7919 ± 0.0032</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>LR C=0.1, cw=None</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>0.7904 ± 0.0032</t>
         </is>
       </c>
     </row>
